--- a/Libraries/Vehicle/Linkage/Subframe_Conn/sm_car_data_Subframe_Conn_ARB_Tr3Ro3.xlsx
+++ b/Libraries/Vehicle/Linkage/Subframe_Conn/sm_car_data_Subframe_Conn_ARB_Tr3Ro3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Linkage\Subframe_Conn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059ACEA4-DE66-4EE4-A4F4-A37A6924DDA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762D5977-784F-4C9E-B759-A4DA426E74A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35220" yWindow="1605" windowWidth="21600" windowHeight="13965" tabRatio="988" xr2:uid="{5C9B011B-FECB-46A4-81D1-C980D278E613}"/>
+    <workbookView xWindow="6945" yWindow="1320" windowWidth="19140" windowHeight="13860" tabRatio="988" xr2:uid="{5C9B011B-FECB-46A4-81D1-C980D278E613}"/>
   </bookViews>
   <sheets>
     <sheet name="BushARB_Tr3Ro3_SLGf_MacP" sheetId="55" r:id="rId1"/>
